--- a/OBJETOS PERDIDOS.xlsx
+++ b/OBJETOS PERDIDOS.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Supervisor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\mpl-objetos-perdidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A02C58-D5F9-4F22-8AAD-1BC6C422F504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D4DC2DE6-1C0E-4728-9E57-CDB0F0BCC1A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11436" windowHeight="2232"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -285,7 +284,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -568,7 +567,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -587,19 +585,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A417CDC-83E3-4B81-B610-1E17EBC87C9B}" name="Tabla1" displayName="Tabla1" ref="A1:J2" insertRow="1" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2">
-  <autoFilter ref="A1:J2" xr:uid="{9A417CDC-83E3-4B81-B610-1E17EBC87C9B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J2" insertRow="1" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:J2"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{BC39D4B1-542D-4985-8F8A-550EDBC0CC60}" name="Acta de recepcion" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{68BB2477-0D7A-406B-94A1-C0306D6E6981}" name="Fecha de reporte" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{186F3A4B-893B-4C40-AFCF-B781588F0100}" name="Descripción"/>
-    <tableColumn id="4" xr3:uid="{F1C94E8B-8B9F-4591-935C-0D8FF46D7ACF}" name="Categoría"/>
-    <tableColumn id="5" xr3:uid="{AAE1E957-4FF4-42F9-98E3-4C55F237AB29}" name="Lugar de referencia"/>
-    <tableColumn id="6" xr3:uid="{D8E266B1-602C-4BA2-AFDC-82DF3E7D742F}" name="Operador que recepciona "/>
-    <tableColumn id="7" xr3:uid="{4BFA7336-FA4D-4397-BAB2-84A0324A5F9F}" name="Acta de entrega"/>
-    <tableColumn id="8" xr3:uid="{B14CDC37-5CB8-4ABA-94B3-D23B1E9626C9}" name="Estado"/>
-    <tableColumn id="9" xr3:uid="{29EAED66-7D76-4738-B6EE-BF61BEB576EB}" name="fecha de entrega"/>
-    <tableColumn id="10" xr3:uid="{50361EDC-8B45-4A4B-9732-5F9C55C26D72}" name="Observaciones"/>
+    <tableColumn id="1" name="Acta de recepcion" dataDxfId="1"/>
+    <tableColumn id="2" name="Fecha de reporte" dataDxfId="0"/>
+    <tableColumn id="3" name="Descripción"/>
+    <tableColumn id="4" name="Categoría"/>
+    <tableColumn id="5" name="Lugar de referencia"/>
+    <tableColumn id="6" name="Operador que recepciona "/>
+    <tableColumn id="7" name="Acta de entrega"/>
+    <tableColumn id="8" name="Estado"/>
+    <tableColumn id="9" name="fecha de entrega"/>
+    <tableColumn id="10" name="Observaciones"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -901,24 +899,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B83B11C-2663-488F-B802-DDE197434E1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.109375" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="10" max="10" width="28.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="28.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -950,8 +948,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -977,7 +975,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
@@ -1006,7 +1004,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>21</v>
       </c>
@@ -1031,7 +1029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>25</v>
       </c>
@@ -1058,7 +1056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>27</v>
       </c>
@@ -1087,7 +1085,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>30</v>
       </c>
@@ -1113,7 +1111,7 @@
       <c r="I8" s="10"/>
       <c r="J8" s="11"/>
     </row>
-    <row r="9" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
@@ -1142,7 +1140,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>36</v>
       </c>
@@ -1171,7 +1169,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>40</v>
       </c>
@@ -1200,7 +1198,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>49</v>
       </c>
@@ -1229,7 +1227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
@@ -1258,7 +1256,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -1287,7 +1285,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>56</v>
       </c>
@@ -1316,7 +1314,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>59</v>
       </c>
@@ -1345,7 +1343,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>63</v>
       </c>
@@ -1371,7 +1369,7 @@
       <c r="I17" s="10"/>
       <c r="J17" s="11"/>
     </row>
-    <row r="18" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>65</v>
       </c>
@@ -1395,7 +1393,7 @@
       <c r="I18" s="10"/>
       <c r="J18" s="11"/>
     </row>
-    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>66</v>
       </c>
@@ -1421,7 +1419,7 @@
       <c r="I19" s="10"/>
       <c r="J19" s="11"/>
     </row>
-    <row r="20" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>79</v>
       </c>
@@ -1447,7 +1445,7 @@
       <c r="I20" s="10"/>
       <c r="J20" s="11"/>
     </row>
-    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="19"/>
       <c r="C21" s="20"/>
@@ -1459,7 +1457,7 @@
       <c r="I21" s="10"/>
       <c r="J21" s="11"/>
     </row>
-    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10"/>
@@ -1471,7 +1469,7 @@
       <c r="I22" s="10"/>
       <c r="J22" s="11"/>
     </row>
-    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="10"/>
@@ -1483,7 +1481,7 @@
       <c r="I23" s="10"/>
       <c r="J23" s="11"/>
     </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="10"/>
@@ -1495,7 +1493,7 @@
       <c r="I24" s="10"/>
       <c r="J24" s="11"/>
     </row>
-    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="10"/>
@@ -1507,7 +1505,7 @@
       <c r="I25" s="10"/>
       <c r="J25" s="11"/>
     </row>
-    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
       <c r="C26" s="10"/>
@@ -1519,7 +1517,7 @@
       <c r="I26" s="10"/>
       <c r="J26" s="11"/>
     </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
       <c r="C27" s="10"/>
@@ -1531,7 +1529,7 @@
       <c r="I27" s="10"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10"/>
@@ -1543,7 +1541,7 @@
       <c r="I28" s="10"/>
       <c r="J28" s="11"/>
     </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="10"/>
@@ -1555,7 +1553,7 @@
       <c r="I29" s="10"/>
       <c r="J29" s="11"/>
     </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
       <c r="C30" s="14"/>
@@ -1570,13 +1568,13 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H2 H31:H1048576" xr:uid="{8CDD552F-4341-4D3A-A800-9CE4B956F651}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H2 H31:H1048576">
       <formula1>"Entregado"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H30" xr:uid="{3E4B96AA-2BA4-40D9-803A-903C2ED5E26B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H30">
       <formula1>$L$4:$L$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D30" xr:uid="{06B27ED9-2D0A-4095-9D71-C733DC776AA6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D30">
       <formula1>$L$9:$L$16</formula1>
     </dataValidation>
   </dataValidations>
